--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-141159</t>
+          <t>I-141242</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,17 +508,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.6494978</t>
+          <t>-13.6497088</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-73.3632132</t>
+          <t>-73.3639174</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jr. Astohuaraca / Jr. Bolognesi</t>
+          <t>Jirón 28 de Julio / Jirón Bolognesi</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-141242</t>
+          <t>I-541272</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.6497088</t>
+          <t>-13.6522228</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-73.3639174</t>
+          <t>-73.3578899</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. 28 de Julio / Jr. Bolognesi</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-541272</t>
+          <t>I-140822</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.6522228</t>
+          <t>-13.6513156</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-73.3578899</t>
+          <t>-73.3692743</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avenida Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-541273</t>
+          <t>I-541422</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.652271</t>
+          <t>-13.6561243</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-73.3580746</t>
+          <t>-73.3004367</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-541410</t>
+          <t>I-541421</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,22 +716,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-13.6701605</t>
+          <t>-13.6580806</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-73.2873156</t>
+          <t>-73.3003696</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-541411</t>
+          <t>I-541420</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-13.6706349</t>
+          <t>-13.6660299</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-73.2875325</t>
+          <t>-73.2972702</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-541413</t>
+          <t>I-541419</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -820,25 +820,701 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-13.6706409</t>
+          <t>-13.6681794</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-73.2877241</t>
+          <t>-73.2988957</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-541417</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-13.6627199</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-73.2990298</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-541412</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-13.6727868</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-73.2888368</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-541409</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-13.6720785</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-73.2880919</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-541408</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-13.6683521</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-73.2930833</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-541407</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-13.6708619</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-73.290621</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-541406</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-13.6736636</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-73.2892022</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-541405</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-13.6719439</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-73.2870171</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-541379</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-13.6807243</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-73.2755649</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-541383</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-13.6821661</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-73.2639371</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-541392</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-13.6940665</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-73.2863858</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-541393</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-13.6808688</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-73.2920252</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-541394</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-13.6794362</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-73.2871905</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-541396</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-13.6732494</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-73.2926497</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>030213</t>
         </is>

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1520,6 +1520,266 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-140823</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-13.6515737</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-73.3702751</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Avenida Bolognesi / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-541380</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-13.6823811</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-73.2716713</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-541382</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-13.6834865</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-73.2677647</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-541391</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-13.6897002</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-73.2943064</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-541395</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-13.6776191</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-73.2874683</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,6 +1780,58 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-140824</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SAN JERONIMO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-13.6519447</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-73.3716585</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Avenida Bolognesi / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>030213</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-141242</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-13.6497088</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-541272</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-13.6522228</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-140822</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-13.6513156</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-541422</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-13.6561243</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-541421</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-13.6580806</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-541420</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-13.6660299</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-541419</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-13.6681794</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-541417</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-13.6627199</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-541412</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-13.6727868</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-541409</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-13.6720785</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-541408</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-13.6683521</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-541407</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-13.6708619</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-541406</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-13.6736636</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-541405</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-13.6719439</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-541379</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-13.6807243</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-541383</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-13.6821661</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-541392</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-13.6940665</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-541393</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-13.6808688</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-541394</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-13.6794362</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-541396</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-13.6732494</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-140823</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-13.6515737</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-541380</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-13.6823811</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-541382</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-13.6834865</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-541391</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-13.6897002</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-541395</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-13.6776191</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>030213</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ANDAHUAYLAS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SAN_JERONIMO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-140824</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>030213</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ANDAHUAYLAS</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>SAN JERONIMO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-13.6519447</t>
@@ -1824,11 +1694,6 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>030213</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SAN_JERONIMO</t>
+          <t>SAN JERONIMO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\PI2026\Intersecciones\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2669545-D9B4-432B-B011-687C30B2E325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7573B5D-81CC-4508-BE9E-6362378C0352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="110">
   <si>
     <t>ubigeo_gestor</t>
   </si>
@@ -64,12 +77,6 @@
     <t>I-141242</t>
   </si>
   <si>
-    <t>-13.6497088</t>
-  </si>
-  <si>
-    <t>-73.3639174</t>
-  </si>
-  <si>
     <t>Jirón 28 de Julio / Jirón Bolognesi</t>
   </si>
   <si>
@@ -79,12 +86,6 @@
     <t>I-541272</t>
   </si>
   <si>
-    <t>-13.6522228</t>
-  </si>
-  <si>
-    <t>-73.3578899</t>
-  </si>
-  <si>
     <t>Calle s / n / Calle s / n</t>
   </si>
   <si>
@@ -196,12 +197,6 @@
     <t>I-541405</t>
   </si>
   <si>
-    <t>-13.6719439</t>
-  </si>
-  <si>
-    <t>-73.2870171</t>
-  </si>
-  <si>
     <t>I-541379</t>
   </si>
   <si>
@@ -304,12 +299,6 @@
     <t>I-140824</t>
   </si>
   <si>
-    <t>-13.6519447</t>
-  </si>
-  <si>
-    <t>-73.3716585</t>
-  </si>
-  <si>
     <t>I-141236</t>
   </si>
   <si>
@@ -347,6 +336,33 @@
   </si>
   <si>
     <t>I-141127</t>
+  </si>
+  <si>
+    <t>Jr. Chaski calle con Ca. s/n</t>
+  </si>
+  <si>
+    <t>Jr. San Martin con Ca. s/n</t>
+  </si>
+  <si>
+    <t>Ca. Doble con Ca. Doble</t>
+  </si>
+  <si>
+    <t>Jr. Bolognesi con Ca. s/n</t>
+  </si>
+  <si>
+    <t>Jr. Chaski calle con Jr. Astuhuaraca</t>
+  </si>
+  <si>
+    <t>Calle s / n</t>
+  </si>
+  <si>
+    <t>Jr. Asthuaraca con calle s/n</t>
+  </si>
+  <si>
+    <t>Carr. Ancatira central con ca. s/n</t>
+  </si>
+  <si>
+    <t>Jr. Eusevio Reynaga con Ca. s/n</t>
   </si>
 </sst>
 </file>
@@ -734,17 +750,17 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2">
+        <v>-13.649708800000001</v>
+      </c>
+      <c r="G2">
+        <v>-73.363917400000005</v>
+      </c>
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,19 +777,19 @@
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <v>-13.652222800000001</v>
+      </c>
+      <c r="G3">
+        <v>-73.357889900000004</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,19 +806,19 @@
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -819,19 +835,19 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,19 +864,19 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,19 +893,19 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,19 +922,19 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,19 +951,19 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -964,19 +980,19 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -993,19 +1009,19 @@
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -1022,19 +1038,19 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -1051,19 +1067,19 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -1080,19 +1096,19 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1109,19 +1125,19 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="F15">
+        <v>-13.6719439</v>
+      </c>
+      <c r="G15">
+        <v>-73.2870171</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1138,19 +1154,19 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1167,19 +1183,19 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -1196,19 +1212,19 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1225,19 +1241,19 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1254,19 +1270,19 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1283,19 +1299,19 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1312,19 +1328,19 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1341,19 +1357,19 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1370,19 +1386,19 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1399,19 +1415,19 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1428,19 +1444,19 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
@@ -1457,19 +1473,19 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" t="s">
-        <v>94</v>
-      </c>
-      <c r="G27" t="s">
-        <v>95</v>
+        <v>87</v>
+      </c>
+      <c r="F27">
+        <v>-13.6519447</v>
+      </c>
+      <c r="G27">
+        <v>-73.371658499999995</v>
       </c>
       <c r="H27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
@@ -1486,19 +1502,19 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F28">
-        <v>-13.653628899999999</v>
+        <v>-13.6543379</v>
       </c>
       <c r="G28">
-        <v>-73.3644465</v>
+        <v>-73.364348199999995</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
@@ -1515,19 +1531,19 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F29">
-        <v>-13.650657199999999</v>
+        <v>-13.6509213</v>
       </c>
       <c r="G29">
-        <v>-73.3644867</v>
+        <v>-73.365284799999998</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
@@ -1544,19 +1560,19 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F30">
-        <v>-13.6527548</v>
+        <v>-13.652865500000001</v>
       </c>
       <c r="G30">
-        <v>-73.365405300000006</v>
+        <v>-73.365349100000003</v>
       </c>
       <c r="H30" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
@@ -1573,19 +1589,19 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F31">
-        <v>-13.654376900000001</v>
+        <v>-13.653658800000001</v>
       </c>
       <c r="G31">
-        <v>-73.366016599999995</v>
+        <v>-73.366022200000003</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
@@ -1602,19 +1618,19 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F32">
-        <v>-13.6499533</v>
+        <v>-13.6501772</v>
       </c>
       <c r="G32">
-        <v>-73.364753699999994</v>
+        <v>-73.365520200000006</v>
       </c>
       <c r="H32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I32" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
@@ -1631,19 +1647,19 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F33">
-        <v>-13.6499778</v>
+        <v>-13.6502114</v>
       </c>
       <c r="G33">
-        <v>-73.362241800000007</v>
+        <v>-73.363001100000005</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="I33" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -1660,19 +1676,19 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F34">
-        <v>-13.652620900000001</v>
+        <v>-13.652329099999999</v>
       </c>
       <c r="G34">
-        <v>-73.364698300000001</v>
+        <v>-73.364777500000002</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -1689,19 +1705,19 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F35">
-        <v>-13.662192599999999</v>
+        <v>-13.662432300000001</v>
       </c>
       <c r="G35">
-        <v>-73.348223399999995</v>
+        <v>-73.349403300000006</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -1718,19 +1734,19 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F36">
-        <v>-13.6527292</v>
+        <v>-13.652491100000001</v>
       </c>
       <c r="G36">
-        <v>-73.360182100000003</v>
+        <v>-73.360438900000005</v>
       </c>
       <c r="H36" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1747,19 +1763,19 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37">
+        <v>-13.663387999999999</v>
+      </c>
+      <c r="G37">
+        <v>-73.3489632</v>
+      </c>
+      <c r="H37" t="s">
         <v>106</v>
       </c>
-      <c r="F37">
-        <v>-13.663192199999999</v>
-      </c>
-      <c r="G37">
-        <v>-73.348048399999996</v>
-      </c>
-      <c r="H37" t="s">
-        <v>21</v>
-      </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1776,19 +1792,19 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F38">
-        <v>-13.652775699999999</v>
+        <v>-13.652805300000001</v>
       </c>
       <c r="G38">
-        <v>-73.3705669</v>
+        <v>-73.3702969</v>
       </c>
       <c r="H38" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1805,19 +1821,19 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F39">
-        <v>-13.6553176</v>
+        <v>-13.655283300000001</v>
       </c>
       <c r="G39">
-        <v>-73.361318400000002</v>
+        <v>-73.361314100000001</v>
       </c>
       <c r="H39" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="I39" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
+++ b/Intersecciones/excels/APURIMAC-ANDAHUAYLAS-SAN_JERONIMO.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-141242</t>
+          <t>I-730489</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-13.6497088</t>
+          <t>-13.6526209</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-73.3639174</t>
+          <t>-73.3646983</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jirón 28 de Julio / Jirón Bolognesi</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-541272</t>
+          <t>I-642200</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-13.657631</t>
+          <t>-13.6621926</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-73.351626</t>
+          <t>-73.3482234</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jr. Andres Avelino Caçeres / Salida a Poltoccsa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-140822</t>
+          <t>I-641935</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-13.6513156</t>
+          <t>-13.653833</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-73.3692743</t>
+          <t>-73.369876</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Bolognesi / Calle s / n</t>
+          <t>Av. Leoncio Prado / Jr. 7 junio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-541379</t>
+          <t>I-541396</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-13.6807243</t>
+          <t>-13.6732494</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-73.2755649</t>
+          <t>-73.2926497</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-541383</t>
+          <t>I-541395</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-13.6821661</t>
+          <t>-13.6776191</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-73.2639371</t>
+          <t>-73.2874683</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-541392</t>
+          <t>I-541394</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-13.6940665</t>
+          <t>-13.6794362</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-73.2863858</t>
+          <t>-73.2871905</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-541394</t>
+          <t>I-541392</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-13.6794362</t>
+          <t>-13.6940665</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-73.2871905</t>
+          <t>-73.2863858</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-541396</t>
+          <t>I-541391</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-13.6732494</t>
+          <t>-13.6897002</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-73.2926497</t>
+          <t>-73.2943064</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-140823</t>
+          <t>I-541383</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-13.6515737</t>
+          <t>-13.6821661</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-73.3702751</t>
+          <t>-73.2639371</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Bolognesi / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-541380</t>
+          <t>I-541382</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-13.6823811</t>
+          <t>-13.6834865</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-73.2716713</t>
+          <t>-73.2677647</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-541382</t>
+          <t>I-541380</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-13.6834865</t>
+          <t>-13.6823811</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-73.2677647</t>
+          <t>-73.2716713</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-541391</t>
+          <t>I-541379</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-13.6897002</t>
+          <t>-13.6807243</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-73.2943064</t>
+          <t>-73.2755649</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,27 +1614,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-541395</t>
+          <t>I-541272</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-13.6776191</t>
+          <t>-13.657631</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-73.2874683</t>
+          <t>-73.351626</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jr. Andres Avelino Caçeres / Salida a Poltoccsa</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-140824</t>
+          <t>I-141242</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-13.6519447</t>
+          <t>-13.6497088</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-73.3716585</t>
+          <t>-73.3639174</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Avenida Bolognesi / Calle s / n</t>
+          <t>Jirón 28 de Julio / Jirón Bolognesi</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-13.6543379</t>
+          <t>-13.6536289</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-73.3643482</t>
+          <t>-73.3644465</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-141097</t>
+          <t>I-141232</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-13.6509213</t>
+          <t>-13.6499778</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-73.3652848</t>
+          <t>-73.3622418</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Jr. Chaski calle con Ca. s/n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-141211</t>
+          <t>I-141213</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-13.650832</t>
+          <t>-13.653114</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-73.367674</t>
+          <t>-73.362002</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Jr. Arica / Prolog. Bolognesi</t>
+          <t xml:space="preserve">Jr. Astuhuaraca / Jr. Eusebio Reynaga </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-641935</t>
+          <t>I-141211</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-13.653833</t>
+          <t>-13.650832</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-73.369876</t>
+          <t>-73.367674</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Av. Leoncio Prado / Jr. 7 junio</t>
+          <t>Jr. Arica / Prolog. Bolognesi</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-141099</t>
+          <t>I-141200</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-13.6501772</t>
+          <t>-13.6527292</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-73.3655202</t>
+          <t>-73.3601821</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Jr. Bolognesi con Ca. s/n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-141232</t>
+          <t>I-141127</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-13.6502114</t>
+          <t>-13.650482</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-73.3630011</t>
+          <t>-73.361346</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Jr. Chaski calle con Jr. Astuhuaraca</t>
+          <t>Jr. Alfonso Ugarte / Jr. Anccohuayllo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-730489</t>
+          <t>I-141099</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-13.6523291</t>
+          <t>-13.6499533</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-73.3647775</t>
+          <t>-73.3647537</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,17 +2037,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-642200</t>
+          <t>I-141097</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-13.6624323</t>
+          <t>-13.6506572</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-73.3494033</t>
+          <t>-73.3644867</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2084,22 +2084,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-141200</t>
+          <t>I-140853</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-13.6524911</t>
+          <t>-13.6527757</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-73.3604389</t>
+          <t>-73.3705669</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-141213</t>
+          <t>I-140824</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-13.653114</t>
+          <t>-13.6519447</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-73.362002</t>
+          <t>-73.3716585</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jr. Astuhuaraca / Jr. Eusebio Reynaga </t>
+          <t>Avenida Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-140853</t>
+          <t>I-140823</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-13.6528053</t>
+          <t>-13.6515737</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-73.3702969</t>
+          <t>-73.3702751</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>calle sn / calle s/n</t>
+          <t>Avenida Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-141127</t>
+          <t>I-140822</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-13.650482</t>
+          <t>-13.6513156</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-73.361346</t>
+          <t>-73.3692743</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Jr. Alfonso Ugarte / Jr. Anccohuayllo</t>
+          <t>Avenida Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
